--- a/cet4/result/56_职场女王_从零到巅峰的逆袭/56_职场女王_从零到巅峰的逆袭_学习版.xlsx
+++ b/cet4/result/56_职场女王_从零到巅峰的逆袭/56_职场女王_从零到巅峰的逆袭_学习版.xlsx
@@ -397,787 +397,689 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D48"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>scarf</v>
       </c>
       <c r="B2" t="str">
-        <v>scarf</v>
+        <v>/skɑːrf/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D2" t="str">
         <v>围巾</v>
       </c>
-      <c r="D2" t="str">
-        <v>scarf(围巾)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>waist</v>
       </c>
       <c r="B3" t="str">
-        <v>waist</v>
+        <v>/weɪst/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>腰部</v>
       </c>
-      <c r="D3" t="str">
-        <v>waist(腰部)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>typist</v>
       </c>
       <c r="B4" t="str">
-        <v>typist</v>
+        <v>/ˈtaɪpɪst/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>打字员</v>
       </c>
-      <c r="D4" t="str">
-        <v>typist(打字员)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>centre</v>
       </c>
       <c r="B5" t="str">
-        <v>centre</v>
+        <v>/ˈsentər/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D5" t="str">
         <v>中心</v>
       </c>
-      <c r="D5" t="str">
-        <v>centre(中心)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>capital</v>
       </c>
       <c r="B6" t="str">
-        <v>capital</v>
+        <v>/ˈkæpɪtl/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>资本</v>
       </c>
-      <c r="D6" t="str">
-        <v>capital(资本)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>brittle</v>
       </c>
       <c r="B7" t="str">
-        <v>brittle</v>
+        <v>/ˈbrɪtl/</v>
       </c>
       <c r="C7" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>易碎的</v>
       </c>
-      <c r="D7" t="str">
-        <v>brittle(易碎的)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>Italian</v>
       </c>
       <c r="B8" t="str">
-        <v>Italian</v>
+        <v>/ɪˈtæliən/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>意大利语</v>
       </c>
-      <c r="D8" t="str">
-        <v>Italian(意大利语)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>chemistry</v>
       </c>
       <c r="B9" t="str">
-        <v>chemistry</v>
+        <v>/ˈkemɪstri/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>化学</v>
       </c>
-      <c r="D9" t="str">
-        <v>chemistry(化学)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>junior</v>
       </c>
       <c r="B10" t="str">
-        <v>junior</v>
+        <v>/ˈdʒuːniər/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>下级的</v>
       </c>
-      <c r="D10" t="str">
-        <v>junior(下级的)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>stormy</v>
       </c>
       <c r="B11" t="str">
-        <v>stormy</v>
+        <v>/ˈstɔːrmi/</v>
       </c>
       <c r="C11" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>暴风雨的</v>
       </c>
-      <c r="D11" t="str">
-        <v>stormy(暴风雨的)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>ridiculous</v>
       </c>
       <c r="B12" t="str">
-        <v>ridiculous</v>
+        <v>/rɪˈdɪkjələs/</v>
       </c>
       <c r="C12" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>可笑的</v>
       </c>
-      <c r="D12" t="str">
-        <v>ridiculous(可笑的)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>proposal</v>
       </c>
       <c r="B13" t="str">
-        <v>proposal</v>
+        <v>/prəˈpoʊzl/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>提议</v>
       </c>
-      <c r="D13" t="str">
-        <v>proposal(提议)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>frequent</v>
       </c>
       <c r="B14" t="str">
-        <v>frequent</v>
+        <v>/ˈfriːkwənt; friˈkwent/</v>
       </c>
       <c r="C14" t="str">
+        <v>vt./adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>频繁的</v>
       </c>
-      <c r="D14" t="str">
-        <v>frequent(频繁的)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>opponent</v>
       </c>
       <c r="B15" t="str">
-        <v>opponent</v>
+        <v>/əˈpoʊnənt/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D15" t="str">
         <v>对手</v>
       </c>
-      <c r="D15" t="str">
-        <v>opponent(对手)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>material</v>
       </c>
       <c r="B16" t="str">
-        <v>material</v>
+        <v>/məˈtɪriəl/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>材料</v>
       </c>
-      <c r="D16" t="str">
-        <v>material(材料)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>somebody</v>
       </c>
       <c r="B17" t="str">
-        <v>somebody</v>
+        <v>/ˈsʌmbədi/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D17" t="str">
         <v>某人</v>
       </c>
-      <c r="D17" t="str">
-        <v>somebody(某人)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>respect</v>
       </c>
       <c r="B18" t="str">
-        <v>respect</v>
+        <v>/rɪˈspekt/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D18" t="str">
         <v>尊重</v>
       </c>
-      <c r="D18" t="str">
-        <v>respect(尊重)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>rehearsal</v>
       </c>
       <c r="B19" t="str">
-        <v>rehearsal</v>
+        <v>/rɪˈhɜːrsl/</v>
       </c>
       <c r="C19" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>排练</v>
       </c>
-      <c r="D19" t="str">
-        <v>rehearsal(排练)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>determination</v>
       </c>
       <c r="B20" t="str">
-        <v>determination</v>
+        <v>/dɪˌtɜːrmɪˈneɪʃn/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>决心</v>
       </c>
-      <c r="D20" t="str">
-        <v>determination(决心)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>earnest</v>
       </c>
       <c r="B21" t="str">
-        <v>earnest</v>
+        <v>/ˈɜːrnɪst/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>认真的</v>
       </c>
-      <c r="D21" t="str">
-        <v>earnest(认真的)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>private</v>
       </c>
       <c r="B22" t="str">
-        <v>private</v>
+        <v>/ˈpraɪvət/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D22" t="str">
         <v>私人的</v>
       </c>
-      <c r="D22" t="str">
-        <v>private(私人的)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>language</v>
       </c>
       <c r="B23" t="str">
-        <v>language</v>
+        <v>/ˈlæŋɡwɪdʒ/</v>
       </c>
       <c r="C23" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>语言</v>
       </c>
-      <c r="D23" t="str">
-        <v>language(语言)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>vivid</v>
       </c>
       <c r="B24" t="str">
-        <v>vivid</v>
+        <v>/ˈvɪvɪd/</v>
       </c>
       <c r="C24" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D24" t="str">
         <v>生动的</v>
       </c>
-      <c r="D24" t="str">
-        <v>vivid(生动的)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>illegal</v>
       </c>
       <c r="B25" t="str">
-        <v>illegal</v>
+        <v>/ɪˈliːɡl/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D25" t="str">
         <v>非法的</v>
       </c>
-      <c r="D25" t="str">
-        <v>illegal(非法的)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>merit</v>
       </c>
       <c r="B26" t="str">
-        <v>merit</v>
+        <v>/ˈmerɪt/</v>
       </c>
       <c r="C26" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D26" t="str">
         <v>价值</v>
       </c>
-      <c r="D26" t="str">
-        <v>merit(价值)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>series</v>
       </c>
       <c r="B27" t="str">
-        <v>series</v>
+        <v>/ˈsɪriːz/</v>
       </c>
       <c r="C27" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>系列</v>
       </c>
-      <c r="D27" t="str">
-        <v>series(系列)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>provision</v>
       </c>
       <c r="B28" t="str">
-        <v>capital</v>
+        <v>/prəˈvɪʒn/</v>
       </c>
       <c r="C28" t="str">
-        <v>资本</v>
+        <v>n./vt.</v>
       </c>
       <c r="D28" t="str">
-        <v>capital(资本)📢</v>
+        <v>条款</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>pioneer</v>
       </c>
       <c r="B29" t="str">
-        <v>provision</v>
+        <v>/ˌpaɪəˈnɪr/</v>
       </c>
       <c r="C29" t="str">
-        <v>条款</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D29" t="str">
-        <v>provision(条款)📢</v>
+        <v>先锋</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>reform</v>
       </c>
       <c r="B30" t="str">
-        <v>centre</v>
+        <v>/rɪˈfɔːrm/</v>
       </c>
       <c r="C30" t="str">
-        <v>中心</v>
+        <v>n./v./adj.</v>
       </c>
       <c r="D30" t="str">
-        <v>centre(中心)📢</v>
+        <v>改革</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>orderly</v>
       </c>
       <c r="B31" t="str">
-        <v>pioneer</v>
+        <v>/ˈɔːrdərli/</v>
       </c>
       <c r="C31" t="str">
-        <v>先锋</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D31" t="str">
-        <v>pioneer(先锋)📢</v>
+        <v>有秩序的</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>manual</v>
       </c>
       <c r="B32" t="str">
-        <v>stormy</v>
+        <v>/ˈmænjuəl/</v>
       </c>
       <c r="C32" t="str">
-        <v>暴风雨的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D32" t="str">
-        <v>stormy(暴风雨的)📢</v>
+        <v>手册</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>wide</v>
       </c>
       <c r="B33" t="str">
-        <v>reform</v>
+        <v>/waɪd/</v>
       </c>
       <c r="C33" t="str">
-        <v>改革</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D33" t="str">
-        <v>reform(改革)📢</v>
+        <v>广泛的</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>impose</v>
       </c>
       <c r="B34" t="str">
-        <v>orderly</v>
+        <v>/ɪmˈpoʊz/</v>
       </c>
       <c r="C34" t="str">
-        <v>有秩序的</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D34" t="str">
-        <v>orderly(有秩序的)📢</v>
+        <v>强加</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>monument</v>
       </c>
       <c r="B35" t="str">
-        <v>manual</v>
+        <v>/ˈmɑːnjumənt/</v>
       </c>
       <c r="C35" t="str">
-        <v>手册</v>
+        <v>n./vt.</v>
       </c>
       <c r="D35" t="str">
-        <v>manual(手册)📢</v>
+        <v>纪念碑</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>drop</v>
       </c>
       <c r="B36" t="str">
-        <v>wide</v>
+        <v>/drɑːp/</v>
       </c>
       <c r="C36" t="str">
-        <v>广泛的</v>
+        <v>n./v.</v>
       </c>
       <c r="D36" t="str">
-        <v>wide(广泛的)📢</v>
+        <v>放弃</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>puzzle</v>
       </c>
       <c r="B37" t="str">
-        <v>vivid</v>
+        <v>/ˈpʌzl/</v>
       </c>
       <c r="C37" t="str">
-        <v>生动的</v>
+        <v>n./v.</v>
       </c>
       <c r="D37" t="str">
-        <v>vivid(生动的)📢</v>
+        <v>谜</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>ghost</v>
       </c>
       <c r="B38" t="str">
-        <v>Italian</v>
+        <v>/ɡoʊst/</v>
       </c>
       <c r="C38" t="str">
-        <v>意大利</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>Italian(意大利)📢</v>
+        <v>幽灵</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>fox</v>
       </c>
       <c r="B39" t="str">
-        <v>scarf</v>
+        <v>/fɑːks/</v>
       </c>
       <c r="C39" t="str">
-        <v>围巾</v>
+        <v>n./v.</v>
       </c>
       <c r="D39" t="str">
-        <v>scarf(围巾)📢</v>
+        <v>狐狸</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>melon</v>
       </c>
       <c r="B40" t="str">
-        <v>impose</v>
+        <v>/ˈmelən/</v>
       </c>
       <c r="C40" t="str">
-        <v>强加</v>
+        <v>n.</v>
       </c>
       <c r="D40" t="str">
-        <v>impose(强加)📢</v>
+        <v>瓜</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>sausage</v>
       </c>
       <c r="B41" t="str">
-        <v>monument</v>
+        <v>/ˈsɔːsɪdʒ/</v>
       </c>
       <c r="C41" t="str">
-        <v>纪念碑</v>
+        <v>n.</v>
       </c>
       <c r="D41" t="str">
-        <v>monument(纪念碑)📢</v>
+        <v>香肠</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>cook</v>
       </c>
       <c r="B42" t="str">
-        <v>drop</v>
+        <v>/kʊk/</v>
       </c>
       <c r="C42" t="str">
-        <v>放弃</v>
+        <v>n./v.</v>
       </c>
       <c r="D42" t="str">
-        <v>drop(放弃)📢</v>
+        <v>做饭</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>sway</v>
       </c>
       <c r="B43" t="str">
-        <v>puzzle</v>
+        <v>/sweɪ/</v>
       </c>
       <c r="C43" t="str">
-        <v>谜</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D43" t="str">
-        <v>puzzle(谜)📢</v>
+        <v>影响</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>reception</v>
       </c>
       <c r="B44" t="str">
-        <v>ghost</v>
+        <v>/rɪˈsepʃn/</v>
       </c>
       <c r="C44" t="str">
-        <v>幽灵</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>ghost(幽灵)📢</v>
+        <v>招待会</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>gather</v>
       </c>
       <c r="B45" t="str">
-        <v>fox</v>
+        <v>/ˈɡæðər/</v>
       </c>
       <c r="C45" t="str">
-        <v>狐狸</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D45" t="str">
-        <v>fox(狐狸)📢</v>
+        <v>聚集</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>sex</v>
       </c>
       <c r="B46" t="str">
-        <v>chemistry</v>
+        <v>/seks/</v>
       </c>
       <c r="C46" t="str">
-        <v>化学</v>
+        <v>n./vt.</v>
       </c>
       <c r="D46" t="str">
-        <v>chemistry(化学)📢</v>
+        <v>性别</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>sing</v>
       </c>
       <c r="B47" t="str">
-        <v>melon</v>
+        <v>/sɪŋ/</v>
       </c>
       <c r="C47" t="str">
-        <v>瓜</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D47" t="str">
-        <v>melon(瓜)📢</v>
+        <v>唱歌</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>surprising</v>
       </c>
       <c r="B48" t="str">
-        <v>sausage</v>
+        <v>/sərˈpraɪzɪŋ/</v>
       </c>
       <c r="C48" t="str">
-        <v>香肠</v>
+        <v>v./adj.</v>
       </c>
       <c r="D48" t="str">
-        <v>sausage(香肠)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>cook</v>
-      </c>
-      <c r="C49" t="str">
-        <v>做饭</v>
-      </c>
-      <c r="D49" t="str">
-        <v>cook(做饭)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>sway</v>
-      </c>
-      <c r="C50" t="str">
-        <v>影响</v>
-      </c>
-      <c r="D50" t="str">
-        <v>sway(影响)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>reception</v>
-      </c>
-      <c r="C51" t="str">
-        <v>招待会</v>
-      </c>
-      <c r="D51" t="str">
-        <v>reception(招待会)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>gather</v>
-      </c>
-      <c r="C52" t="str">
-        <v>聚集</v>
-      </c>
-      <c r="D52" t="str">
-        <v>gather(聚集)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>sex</v>
-      </c>
-      <c r="C53" t="str">
-        <v>性别</v>
-      </c>
-      <c r="D53" t="str">
-        <v>sex(性别)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>sing</v>
-      </c>
-      <c r="C54" t="str">
-        <v>唱歌</v>
-      </c>
-      <c r="D54" t="str">
-        <v>sing(唱歌)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>surprising</v>
-      </c>
-      <c r="C55" t="str">
         <v>令人惊讶的</v>
-      </c>
-      <c r="D55" t="str">
-        <v>surprising(令人惊讶的)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D48"/>
   </ignoredErrors>
 </worksheet>
 </file>